--- a/Entregables/diagramaYpresupuestoAEYO.xlsx
+++ b/Entregables/diagramaYpresupuestoAEYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9582963325ab153a/Desktop/UNIVERSIDAD/3 SEMESTRE/ALGORITMIA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{6AA38992-F27B-4AEF-8477-3EF2F4969D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D167BDD0-39A1-4292-865A-A96F382E9878}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{6AA38992-F27B-4AEF-8477-3EF2F4969D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1204162A-AB17-40AC-9EFD-05CBB07FC8B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <definedName name="Inicio_del_proyecto" localSheetId="0">Diagrama!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
   <si>
     <t>Descripción</t>
   </si>
@@ -129,9 +130,6 @@
     <t>Investigar como subir la info en GITHUB y organizar el trabajo en MARKDOWN necesarios para establecer una jerarquía como un documento escrito. Recopilar toda la info del trabajo y establecerlo como archivo README.md.</t>
   </si>
   <si>
-    <t>Sin comenzar</t>
-  </si>
-  <si>
     <t>Redacción del primer informe.</t>
   </si>
   <si>
@@ -145,9 +143,6 @@
   </si>
   <si>
     <t>Prioridad 3</t>
-  </si>
-  <si>
-    <t>Bloqueado</t>
   </si>
   <si>
     <t>Redactar actas</t>
@@ -183,12 +178,6 @@
     <t xml:space="preserve">Integración, interfaz y documentación:
 Crear el menú principal, unir todos los módulos, organizar el repositorio en GitHub, subir logo, README y documentación.
 </t>
-  </si>
-  <si>
-    <t>Subir a plataforma el informe final.</t>
-  </si>
-  <si>
-    <t>Redacción del informe final.</t>
   </si>
   <si>
     <t>Realizar pruebas finales.</t>
@@ -247,6 +236,42 @@
   <si>
     <t>Costo</t>
   </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Redacción del informe final y subirlo</t>
+  </si>
+  <si>
+    <t>Sustentación.</t>
+  </si>
+  <si>
+    <t>En curso</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
 </sst>
 </file>
 
@@ -258,7 +283,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,8 +387,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,7 +447,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,21 +580,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFD8D8D8"/>
       </left>
       <right style="thin">
@@ -571,13 +619,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -621,9 +678,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -636,7 +690,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -648,7 +702,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -660,7 +714,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -672,22 +726,19 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyAlignment="1">
@@ -696,18 +747,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -733,13 +784,37 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{8B3C81AA-CFC2-4613-AF67-5221B1EF6BB0}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{86AE5031-1259-421B-BBBE-C3ABB782FA13}"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="171">
     <dxf>
       <font>
         <b/>
@@ -815,6 +890,86 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color theme="0"/>
@@ -832,46 +987,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE5E5E5"/>
-          <bgColor rgb="FFE5E5E5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="5"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF862B98"/>
-          <bgColor rgb="FF862B98"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color theme="0"/>
@@ -889,6 +1004,46 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color theme="0"/>
@@ -906,6 +1061,46 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color theme="0"/>
@@ -980,6 +1175,46 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color theme="0"/>
@@ -999,6 +1234,1287 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF862B98"/>
+          <bgColor rgb="FF862B98"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF2F2F2"/>
           <bgColor rgb="FFF2F2F2"/>
         </patternFill>
@@ -1046,9 +2562,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Diagrama-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="27"/>
-      <tableStyleElement type="firstRowStripe" dxfId="26"/>
-      <tableStyleElement type="secondRowStripe" dxfId="25"/>
+      <tableStyleElement type="headerRow" dxfId="170"/>
+      <tableStyleElement type="firstRowStripe" dxfId="169"/>
+      <tableStyleElement type="secondRowStripe" dxfId="168"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1278,7 +2794,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB989"/>
+  <dimension ref="A1:AV989"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -1289,36 +2805,41 @@
     <col min="6" max="7" width="12.6640625" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="28" width="5.6640625" customWidth="1"/>
+    <col min="29" max="29" width="7.44140625" customWidth="1"/>
+    <col min="30" max="48" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:28" ht="49.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="AC1" s="64" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" ht="49.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="3"/>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="59"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="57"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1327,8 +2848,28 @@
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
-    </row>
-    <row r="3" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC2" s="64"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="57"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="AR2" s="4"/>
+      <c r="AS2" s="4"/>
+      <c r="AT2" s="4"/>
+      <c r="AU2" s="4"/>
+      <c r="AV2" s="4"/>
+    </row>
+    <row r="3" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
         <v>17</v>
@@ -1341,30 +2882,52 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="56"/>
-      <c r="AB3" s="56"/>
-    </row>
-    <row r="4" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="64"/>
+      <c r="AD3" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE3" s="62"/>
+      <c r="AF3" s="62"/>
+      <c r="AG3" s="62"/>
+      <c r="AH3" s="62"/>
+      <c r="AI3" s="62"/>
+      <c r="AJ3" s="62"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="62"/>
+      <c r="AM3" s="62"/>
+      <c r="AN3" s="62"/>
+      <c r="AO3" s="62"/>
+      <c r="AP3" s="62"/>
+      <c r="AQ3" s="62"/>
+      <c r="AR3" s="62"/>
+      <c r="AS3" s="62"/>
+      <c r="AT3" s="62"/>
+      <c r="AU3" s="60"/>
+      <c r="AV3" s="60"/>
+    </row>
+    <row r="4" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1451,8 +3014,82 @@
         <f t="shared" ref="AB4" si="13">AA4+1</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC4" s="64"/>
+      <c r="AD4" s="9">
+        <v>6</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>16</v>
+      </c>
+      <c r="AF4" s="9">
+        <f t="shared" ref="AF4" si="14">AE4+1</f>
+        <v>17</v>
+      </c>
+      <c r="AG4" s="9">
+        <f t="shared" ref="AG4" si="15">AF4+1</f>
+        <v>18</v>
+      </c>
+      <c r="AH4" s="9">
+        <f t="shared" ref="AH4" si="16">AG4+1</f>
+        <v>19</v>
+      </c>
+      <c r="AI4" s="9">
+        <f t="shared" ref="AI4" si="17">AH4+1</f>
+        <v>20</v>
+      </c>
+      <c r="AJ4" s="9">
+        <f t="shared" ref="AJ4" si="18">AI4+1</f>
+        <v>21</v>
+      </c>
+      <c r="AK4" s="9">
+        <f t="shared" ref="AK4" si="19">AJ4+1</f>
+        <v>22</v>
+      </c>
+      <c r="AL4" s="9">
+        <f t="shared" ref="AL4" si="20">AK4+1</f>
+        <v>23</v>
+      </c>
+      <c r="AM4" s="9">
+        <f t="shared" ref="AM4" si="21">AL4+1</f>
+        <v>24</v>
+      </c>
+      <c r="AN4" s="9">
+        <f t="shared" ref="AN4" si="22">AM4+1</f>
+        <v>25</v>
+      </c>
+      <c r="AO4" s="9">
+        <f t="shared" ref="AO4" si="23">AN4+1</f>
+        <v>26</v>
+      </c>
+      <c r="AP4" s="9">
+        <f t="shared" ref="AP4" si="24">AO4+1</f>
+        <v>27</v>
+      </c>
+      <c r="AQ4" s="9">
+        <f t="shared" ref="AQ4" si="25">AP4+1</f>
+        <v>28</v>
+      </c>
+      <c r="AR4" s="9">
+        <v>29</v>
+      </c>
+      <c r="AS4" s="9">
+        <f t="shared" ref="AS4" si="26">AR4+1</f>
+        <v>30</v>
+      </c>
+      <c r="AT4" s="9">
+        <f t="shared" ref="AT4" si="27">AS4+1</f>
+        <v>31</v>
+      </c>
+      <c r="AU4" s="9">
+        <f t="shared" ref="AU4" si="28">AT4+1</f>
+        <v>32</v>
+      </c>
+      <c r="AV4" s="9">
+        <f t="shared" ref="AV4" si="29">AU4+1</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1481,8 +3118,28 @@
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
-    </row>
-    <row r="6" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC5" s="64"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="13"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+    </row>
+    <row r="6" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14"/>
       <c r="B6" s="15" t="s">
         <v>0</v>
@@ -1505,1397 +3162,2380 @@
       <c r="H6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="17" t="str">
-        <f t="shared" ref="I6:AB6" si="14">LEFT(TEXT(I4,"ddd"),1)</f>
-        <v>j</v>
-      </c>
-      <c r="J6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>v</v>
-      </c>
-      <c r="K6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>s</v>
-      </c>
-      <c r="L6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>d</v>
-      </c>
-      <c r="M6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>l</v>
-      </c>
-      <c r="N6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>m</v>
-      </c>
-      <c r="O6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>m</v>
-      </c>
-      <c r="P6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>j</v>
-      </c>
-      <c r="Q6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>v</v>
-      </c>
-      <c r="R6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>s</v>
-      </c>
-      <c r="S6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>d</v>
-      </c>
-      <c r="T6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>l</v>
-      </c>
-      <c r="U6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>m</v>
-      </c>
-      <c r="V6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>m</v>
-      </c>
-      <c r="W6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>j</v>
-      </c>
-      <c r="X6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>v</v>
-      </c>
-      <c r="Y6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>s</v>
-      </c>
-      <c r="Z6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>d</v>
-      </c>
-      <c r="AA6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>l</v>
-      </c>
-      <c r="AB6" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v>m</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="S6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="T6" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="V6" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="W6" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="X6" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA6" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB6" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG6" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH6" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI6" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ6" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK6" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN6" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO6" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP6" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ6" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR6" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS6" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT6" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU6" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV6" s="63" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-    </row>
-    <row r="8" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="21"/>
+      <c r="AI7" s="21"/>
+      <c r="AJ7" s="21"/>
+      <c r="AK7" s="21"/>
+      <c r="AL7" s="21"/>
+      <c r="AM7" s="21"/>
+      <c r="AN7" s="21"/>
+      <c r="AO7" s="21"/>
+      <c r="AP7" s="21"/>
+      <c r="AQ7" s="21"/>
+      <c r="AR7" s="21"/>
+      <c r="AS7" s="21"/>
+      <c r="AT7" s="21"/>
+      <c r="AU7" s="21"/>
+      <c r="AV7" s="21"/>
+    </row>
+    <row r="8" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-    </row>
-    <row r="9" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="33"/>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="33"/>
+      <c r="AR8" s="33"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="33"/>
+    </row>
+    <row r="9" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <v>46093</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="19">
         <v>46093</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <v>1</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-    </row>
-    <row r="10" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="34"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="33"/>
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="33"/>
+      <c r="AH9" s="33"/>
+      <c r="AI9" s="33"/>
+      <c r="AJ9" s="33"/>
+      <c r="AK9" s="33"/>
+      <c r="AL9" s="33"/>
+      <c r="AM9" s="33"/>
+      <c r="AN9" s="33"/>
+      <c r="AO9" s="33"/>
+      <c r="AP9" s="33"/>
+      <c r="AQ9" s="33"/>
+      <c r="AR9" s="33"/>
+      <c r="AS9" s="33"/>
+      <c r="AT9" s="33"/>
+      <c r="AU9" s="33"/>
+      <c r="AV9" s="33"/>
+    </row>
+    <row r="10" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="32">
+        <v>46094</v>
+      </c>
+      <c r="G10" s="32">
+        <v>46098</v>
+      </c>
+      <c r="H10" s="31">
+        <v>5</v>
+      </c>
+      <c r="I10" s="33"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="33"/>
+      <c r="AG10" s="33"/>
+      <c r="AH10" s="33"/>
+      <c r="AI10" s="33"/>
+      <c r="AJ10" s="33"/>
+      <c r="AK10" s="33"/>
+      <c r="AL10" s="33"/>
+      <c r="AM10" s="33"/>
+      <c r="AN10" s="33"/>
+      <c r="AO10" s="33"/>
+      <c r="AP10" s="33"/>
+      <c r="AQ10" s="33"/>
+      <c r="AR10" s="33"/>
+      <c r="AS10" s="33"/>
+      <c r="AT10" s="33"/>
+      <c r="AU10" s="33"/>
+      <c r="AV10" s="33"/>
+    </row>
+    <row r="11" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="19">
+        <v>46103</v>
+      </c>
+      <c r="G11" s="19">
+        <v>46103</v>
+      </c>
+      <c r="H11" s="20">
+        <v>1</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="33"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="33"/>
+      <c r="AO11" s="33"/>
+      <c r="AP11" s="33"/>
+      <c r="AQ11" s="33"/>
+      <c r="AR11" s="33"/>
+      <c r="AS11" s="33"/>
+      <c r="AT11" s="33"/>
+      <c r="AU11" s="33"/>
+      <c r="AV11" s="33"/>
+    </row>
+    <row r="12" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="19">
+        <v>46103</v>
+      </c>
+      <c r="G12" s="19">
+        <v>46107</v>
+      </c>
+      <c r="H12" s="20">
+        <v>5</v>
+      </c>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="33"/>
+      <c r="AH12" s="33"/>
+      <c r="AI12" s="33"/>
+      <c r="AJ12" s="33"/>
+      <c r="AK12" s="33"/>
+      <c r="AL12" s="33"/>
+      <c r="AM12" s="33"/>
+      <c r="AN12" s="33"/>
+      <c r="AO12" s="33"/>
+      <c r="AP12" s="33"/>
+      <c r="AQ12" s="33"/>
+      <c r="AR12" s="33"/>
+      <c r="AS12" s="33"/>
+      <c r="AT12" s="33"/>
+      <c r="AU12" s="33"/>
+      <c r="AV12" s="33"/>
+    </row>
+    <row r="13" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="28">
+        <v>46107</v>
+      </c>
+      <c r="G13" s="19">
+        <v>46107</v>
+      </c>
+      <c r="H13" s="20">
+        <v>1</v>
+      </c>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="33"/>
+      <c r="AE13" s="33"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="33"/>
+      <c r="AH13" s="33"/>
+      <c r="AI13" s="33"/>
+      <c r="AJ13" s="33"/>
+      <c r="AK13" s="33"/>
+      <c r="AL13" s="33"/>
+      <c r="AM13" s="33"/>
+      <c r="AN13" s="33"/>
+      <c r="AO13" s="33"/>
+      <c r="AP13" s="33"/>
+      <c r="AQ13" s="33"/>
+      <c r="AR13" s="33"/>
+      <c r="AS13" s="33"/>
+      <c r="AT13" s="33"/>
+      <c r="AU13" s="33"/>
+      <c r="AV13" s="33"/>
+    </row>
+    <row r="14" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="33"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="33"/>
+      <c r="AH14" s="33"/>
+      <c r="AI14" s="33"/>
+      <c r="AJ14" s="33"/>
+      <c r="AK14" s="33"/>
+      <c r="AL14" s="33"/>
+      <c r="AM14" s="33"/>
+      <c r="AN14" s="33"/>
+      <c r="AO14" s="33"/>
+      <c r="AP14" s="33"/>
+      <c r="AQ14" s="33"/>
+      <c r="AR14" s="33"/>
+      <c r="AS14" s="33"/>
+      <c r="AT14" s="33"/>
+      <c r="AU14" s="33"/>
+      <c r="AV14" s="33"/>
+    </row>
+    <row r="15" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="28">
+        <v>46107</v>
+      </c>
+      <c r="G15" s="19">
+        <v>46108</v>
+      </c>
+      <c r="H15" s="31">
+        <v>2</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="33"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="33"/>
+      <c r="AH15" s="33"/>
+      <c r="AI15" s="33"/>
+      <c r="AJ15" s="33"/>
+      <c r="AK15" s="33"/>
+      <c r="AL15" s="33"/>
+      <c r="AM15" s="33"/>
+      <c r="AN15" s="33"/>
+      <c r="AO15" s="33"/>
+      <c r="AP15" s="33"/>
+      <c r="AQ15" s="33"/>
+      <c r="AR15" s="33"/>
+      <c r="AS15" s="33"/>
+      <c r="AT15" s="33"/>
+      <c r="AU15" s="33"/>
+      <c r="AV15" s="33"/>
+    </row>
+    <row r="16" spans="1:48" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="28">
+        <v>46108</v>
+      </c>
+      <c r="G16" s="19">
+        <v>46111</v>
+      </c>
+      <c r="H16" s="31">
+        <v>4</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="33"/>
+      <c r="AH16" s="33"/>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="33"/>
+      <c r="AK16" s="33"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="33"/>
+      <c r="AN16" s="33"/>
+      <c r="AO16" s="33"/>
+      <c r="AP16" s="33"/>
+      <c r="AQ16" s="33"/>
+      <c r="AR16" s="33"/>
+      <c r="AS16" s="33"/>
+      <c r="AT16" s="33"/>
+      <c r="AU16" s="33"/>
+      <c r="AV16" s="33"/>
+    </row>
+    <row r="17" spans="1:48" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="32">
+        <v>46108</v>
+      </c>
+      <c r="G17" s="32">
+        <v>46111</v>
+      </c>
+      <c r="H17" s="31">
+        <v>4</v>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="33"/>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="33"/>
+      <c r="AH17" s="33"/>
+      <c r="AI17" s="33"/>
+      <c r="AJ17" s="33"/>
+      <c r="AK17" s="33"/>
+      <c r="AL17" s="33"/>
+      <c r="AM17" s="33"/>
+      <c r="AN17" s="33"/>
+      <c r="AO17" s="33"/>
+      <c r="AP17" s="33"/>
+      <c r="AQ17" s="33"/>
+      <c r="AR17" s="33"/>
+      <c r="AS17" s="33"/>
+      <c r="AT17" s="33"/>
+      <c r="AU17" s="33"/>
+      <c r="AV17" s="33"/>
+    </row>
+    <row r="18" spans="1:48" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="32">
+        <v>46108</v>
+      </c>
+      <c r="G18" s="32">
+        <v>46111</v>
+      </c>
+      <c r="H18" s="31">
+        <v>4</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="33"/>
+      <c r="AE18" s="33"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="33"/>
+      <c r="AH18" s="33"/>
+      <c r="AI18" s="33"/>
+      <c r="AJ18" s="33"/>
+      <c r="AK18" s="33"/>
+      <c r="AL18" s="33"/>
+      <c r="AM18" s="33"/>
+      <c r="AN18" s="33"/>
+      <c r="AO18" s="33"/>
+      <c r="AP18" s="33"/>
+      <c r="AQ18" s="33"/>
+      <c r="AR18" s="33"/>
+      <c r="AS18" s="33"/>
+      <c r="AT18" s="33"/>
+      <c r="AU18" s="33"/>
+      <c r="AV18" s="33"/>
+    </row>
+    <row r="19" spans="1:48" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="28">
+        <v>46111</v>
+      </c>
+      <c r="G19" s="19">
+        <v>46112</v>
+      </c>
+      <c r="H19" s="31">
+        <v>2</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="33"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="33"/>
+      <c r="AH19" s="33"/>
+      <c r="AI19" s="33"/>
+      <c r="AJ19" s="33"/>
+      <c r="AK19" s="33"/>
+      <c r="AL19" s="33"/>
+      <c r="AM19" s="33"/>
+      <c r="AN19" s="33"/>
+      <c r="AO19" s="33"/>
+      <c r="AP19" s="33"/>
+      <c r="AQ19" s="33"/>
+      <c r="AR19" s="33"/>
+      <c r="AS19" s="33"/>
+      <c r="AT19" s="33"/>
+      <c r="AU19" s="33"/>
+      <c r="AV19" s="33"/>
+    </row>
+    <row r="20" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C20" s="24"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="33"/>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="33"/>
+      <c r="AH20" s="33"/>
+      <c r="AI20" s="33"/>
+      <c r="AJ20" s="33"/>
+      <c r="AK20" s="33"/>
+      <c r="AL20" s="33"/>
+      <c r="AM20" s="33"/>
+      <c r="AN20" s="33"/>
+      <c r="AO20" s="33"/>
+      <c r="AP20" s="33"/>
+      <c r="AQ20" s="33"/>
+      <c r="AR20" s="33"/>
+      <c r="AS20" s="33"/>
+      <c r="AT20" s="33"/>
+      <c r="AU20" s="33"/>
+      <c r="AV20" s="33"/>
+    </row>
+    <row r="21" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="32">
+        <v>46112</v>
+      </c>
+      <c r="G21" s="32">
+        <v>46112</v>
+      </c>
+      <c r="H21" s="31">
+        <v>1</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33"/>
+      <c r="AH21" s="33"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="33"/>
+      <c r="AK21" s="33"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="33"/>
+      <c r="AN21" s="33"/>
+      <c r="AO21" s="33"/>
+      <c r="AP21" s="33"/>
+      <c r="AQ21" s="33"/>
+      <c r="AR21" s="33"/>
+      <c r="AS21" s="33"/>
+      <c r="AT21" s="33"/>
+      <c r="AU21" s="33"/>
+      <c r="AV21" s="33"/>
+    </row>
+    <row r="22" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D22" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E22" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="32">
+        <v>46112</v>
+      </c>
+      <c r="G22" s="32">
+        <v>46112</v>
+      </c>
+      <c r="H22" s="31">
+        <v>1</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="33"/>
+      <c r="AH22" s="33"/>
+      <c r="AI22" s="33"/>
+      <c r="AJ22" s="33"/>
+      <c r="AK22" s="33"/>
+      <c r="AL22" s="33"/>
+      <c r="AM22" s="33"/>
+      <c r="AN22" s="33"/>
+      <c r="AO22" s="33"/>
+      <c r="AP22" s="33"/>
+      <c r="AQ22" s="33"/>
+      <c r="AR22" s="33"/>
+      <c r="AS22" s="33"/>
+      <c r="AT22" s="33"/>
+      <c r="AU22" s="33"/>
+      <c r="AV22" s="33"/>
+    </row>
+    <row r="23" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="33">
-        <v>46094</v>
-      </c>
-      <c r="G10" s="33">
-        <v>46098</v>
-      </c>
-      <c r="H10" s="32">
-        <v>5</v>
-      </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-    </row>
-    <row r="11" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="28" t="s">
+      <c r="F23" s="32">
+        <v>46112</v>
+      </c>
+      <c r="G23" s="32">
+        <v>46112</v>
+      </c>
+      <c r="H23" s="31">
+        <v>1</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="33"/>
+      <c r="AD23" s="33"/>
+      <c r="AE23" s="33"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="33"/>
+      <c r="AH23" s="33"/>
+      <c r="AI23" s="33"/>
+      <c r="AJ23" s="33"/>
+      <c r="AK23" s="33"/>
+      <c r="AL23" s="33"/>
+      <c r="AM23" s="33"/>
+      <c r="AN23" s="33"/>
+      <c r="AO23" s="33"/>
+      <c r="AP23" s="33"/>
+      <c r="AQ23" s="33"/>
+      <c r="AR23" s="33"/>
+      <c r="AS23" s="33"/>
+      <c r="AT23" s="33"/>
+      <c r="AU23" s="33"/>
+      <c r="AV23" s="33"/>
+    </row>
+    <row r="24" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="33"/>
+      <c r="AE24" s="33"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="33"/>
+      <c r="AH24" s="33"/>
+      <c r="AI24" s="33"/>
+      <c r="AJ24" s="33"/>
+      <c r="AK24" s="33"/>
+      <c r="AL24" s="33"/>
+      <c r="AM24" s="33"/>
+      <c r="AN24" s="33"/>
+      <c r="AO24" s="33"/>
+      <c r="AP24" s="33"/>
+      <c r="AQ24" s="33"/>
+      <c r="AR24" s="33"/>
+      <c r="AS24" s="33"/>
+      <c r="AT24" s="33"/>
+      <c r="AU24" s="33"/>
+      <c r="AV24" s="33"/>
+    </row>
+    <row r="25" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="32">
+        <v>46133</v>
+      </c>
+      <c r="G25" s="32">
+        <v>46175</v>
+      </c>
+      <c r="H25" s="31">
+        <v>42</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="33"/>
+      <c r="AH25" s="33"/>
+      <c r="AI25" s="33"/>
+      <c r="AJ25" s="33"/>
+      <c r="AK25" s="33"/>
+      <c r="AL25" s="33"/>
+      <c r="AM25" s="33"/>
+      <c r="AN25" s="33"/>
+      <c r="AO25" s="33"/>
+      <c r="AP25" s="33"/>
+      <c r="AQ25" s="33"/>
+      <c r="AR25" s="33"/>
+      <c r="AS25" s="33"/>
+      <c r="AT25" s="33"/>
+      <c r="AU25" s="33"/>
+      <c r="AV25" s="33"/>
+    </row>
+    <row r="26" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="32">
+        <v>46148</v>
+      </c>
+      <c r="G26" s="32">
+        <v>46148</v>
+      </c>
+      <c r="H26" s="31">
+        <v>1</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="67"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="33"/>
+      <c r="AH26" s="33"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="33"/>
+      <c r="AK26" s="33"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="33"/>
+      <c r="AP26" s="33"/>
+      <c r="AQ26" s="33"/>
+      <c r="AR26" s="33"/>
+      <c r="AS26" s="33"/>
+      <c r="AT26" s="33"/>
+      <c r="AU26" s="33"/>
+      <c r="AV26" s="33"/>
+    </row>
+    <row r="27" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="33"/>
+      <c r="AH27" s="33"/>
+      <c r="AI27" s="33"/>
+      <c r="AJ27" s="33"/>
+      <c r="AK27" s="33"/>
+      <c r="AL27" s="33"/>
+      <c r="AM27" s="33"/>
+      <c r="AN27" s="33"/>
+      <c r="AO27" s="33"/>
+      <c r="AP27" s="33"/>
+      <c r="AQ27" s="33"/>
+      <c r="AR27" s="33"/>
+      <c r="AS27" s="33"/>
+      <c r="AT27" s="33"/>
+      <c r="AU27" s="33"/>
+      <c r="AV27" s="33"/>
+    </row>
+    <row r="28" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="32">
+        <v>46148</v>
+      </c>
+      <c r="G28" s="32">
+        <v>46148</v>
+      </c>
+      <c r="H28" s="31">
+        <v>1</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="33"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="33"/>
+      <c r="AH28" s="33"/>
+      <c r="AI28" s="33"/>
+      <c r="AJ28" s="33"/>
+      <c r="AK28" s="33"/>
+      <c r="AL28" s="33"/>
+      <c r="AM28" s="33"/>
+      <c r="AN28" s="33"/>
+      <c r="AO28" s="33"/>
+      <c r="AP28" s="33"/>
+      <c r="AQ28" s="33"/>
+      <c r="AR28" s="33"/>
+      <c r="AS28" s="33"/>
+      <c r="AT28" s="33"/>
+      <c r="AU28" s="33"/>
+      <c r="AV28" s="33"/>
+    </row>
+    <row r="29" spans="1:48" ht="72" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D29" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E29" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="32">
+        <v>46160</v>
+      </c>
+      <c r="G29" s="32">
+        <v>46160</v>
+      </c>
+      <c r="H29" s="31">
+        <v>1</v>
+      </c>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="33"/>
+      <c r="AC29" s="33"/>
+      <c r="AD29" s="33"/>
+      <c r="AE29" s="33"/>
+      <c r="AF29" s="33"/>
+      <c r="AG29" s="35"/>
+      <c r="AH29" s="33"/>
+      <c r="AI29" s="33"/>
+      <c r="AJ29" s="33"/>
+      <c r="AK29" s="33"/>
+      <c r="AL29" s="33"/>
+      <c r="AM29" s="33"/>
+      <c r="AN29" s="33"/>
+      <c r="AO29" s="33"/>
+      <c r="AP29" s="33"/>
+      <c r="AQ29" s="33"/>
+      <c r="AR29" s="33"/>
+      <c r="AS29" s="33"/>
+      <c r="AT29" s="33"/>
+      <c r="AU29" s="33"/>
+      <c r="AV29" s="33"/>
+    </row>
+    <row r="30" spans="1:48" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="32">
+        <v>46158</v>
+      </c>
+      <c r="G30" s="32">
+        <v>46158</v>
+      </c>
+      <c r="H30" s="31">
+        <v>1</v>
+      </c>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
+      <c r="AA30" s="33"/>
+      <c r="AB30" s="33"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="33"/>
+      <c r="AE30" s="68"/>
+      <c r="AF30" s="33"/>
+      <c r="AG30" s="33"/>
+      <c r="AH30" s="33"/>
+      <c r="AI30" s="33"/>
+      <c r="AJ30" s="33"/>
+      <c r="AK30" s="33"/>
+      <c r="AL30" s="33"/>
+      <c r="AM30" s="33"/>
+      <c r="AN30" s="33"/>
+      <c r="AO30" s="33"/>
+      <c r="AP30" s="33"/>
+      <c r="AQ30" s="33"/>
+      <c r="AR30" s="33"/>
+      <c r="AS30" s="33"/>
+      <c r="AT30" s="33"/>
+      <c r="AU30" s="33"/>
+      <c r="AV30" s="33"/>
+    </row>
+    <row r="31" spans="1:48" ht="72" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="32">
+        <v>46161</v>
+      </c>
+      <c r="G31" s="32">
+        <v>46161</v>
+      </c>
+      <c r="H31" s="31">
+        <v>1</v>
+      </c>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="33"/>
+      <c r="AC31" s="33"/>
+      <c r="AD31" s="33"/>
+      <c r="AE31" s="33"/>
+      <c r="AF31" s="33"/>
+      <c r="AG31" s="33"/>
+      <c r="AH31" s="68"/>
+      <c r="AI31" s="33"/>
+      <c r="AJ31" s="33"/>
+      <c r="AK31" s="33"/>
+      <c r="AL31" s="33"/>
+      <c r="AM31" s="33"/>
+      <c r="AN31" s="33"/>
+      <c r="AO31" s="33"/>
+      <c r="AP31" s="33"/>
+      <c r="AQ31" s="33"/>
+      <c r="AR31" s="33"/>
+      <c r="AS31" s="33"/>
+      <c r="AT31" s="33"/>
+      <c r="AU31" s="33"/>
+      <c r="AV31" s="33"/>
+    </row>
+    <row r="32" spans="1:48" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="32">
+        <v>46162</v>
+      </c>
+      <c r="G32" s="32">
+        <v>46162</v>
+      </c>
+      <c r="H32" s="31">
+        <v>1</v>
+      </c>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="33"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33"/>
+      <c r="AC32" s="33"/>
+      <c r="AD32" s="33"/>
+      <c r="AE32" s="33"/>
+      <c r="AF32" s="33"/>
+      <c r="AG32" s="33"/>
+      <c r="AH32" s="33"/>
+      <c r="AI32" s="68"/>
+      <c r="AJ32" s="33"/>
+      <c r="AK32" s="33"/>
+      <c r="AL32" s="33"/>
+      <c r="AM32" s="33"/>
+      <c r="AN32" s="33"/>
+      <c r="AO32" s="33"/>
+      <c r="AP32" s="33"/>
+      <c r="AQ32" s="33"/>
+      <c r="AR32" s="33"/>
+      <c r="AS32" s="33"/>
+      <c r="AT32" s="33"/>
+      <c r="AU32" s="33"/>
+      <c r="AV32" s="33"/>
+    </row>
+    <row r="33" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="33"/>
+      <c r="Y33" s="33"/>
+      <c r="Z33" s="33"/>
+      <c r="AA33" s="33"/>
+      <c r="AB33" s="33"/>
+      <c r="AC33" s="33"/>
+      <c r="AD33" s="33"/>
+      <c r="AE33" s="33"/>
+      <c r="AF33" s="33"/>
+      <c r="AG33" s="33"/>
+      <c r="AH33" s="33"/>
+      <c r="AI33" s="33"/>
+      <c r="AJ33" s="33"/>
+      <c r="AK33" s="33"/>
+      <c r="AL33" s="33"/>
+      <c r="AM33" s="33"/>
+      <c r="AN33" s="33"/>
+      <c r="AO33" s="33"/>
+      <c r="AP33" s="33"/>
+      <c r="AQ33" s="33"/>
+      <c r="AR33" s="33"/>
+      <c r="AS33" s="33"/>
+      <c r="AT33" s="33"/>
+      <c r="AU33" s="33"/>
+      <c r="AV33" s="33"/>
+    </row>
+    <row r="34" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="20">
-        <v>46103</v>
-      </c>
-      <c r="G11" s="20">
-        <v>46103</v>
-      </c>
-      <c r="H11" s="21">
+      <c r="F34" s="32">
+        <v>46162</v>
+      </c>
+      <c r="G34" s="32">
+        <v>46170</v>
+      </c>
+      <c r="H34" s="31">
+        <v>9</v>
+      </c>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="33"/>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="67"/>
+      <c r="AK34" s="67"/>
+      <c r="AL34" s="67"/>
+      <c r="AM34" s="67"/>
+      <c r="AN34" s="67"/>
+      <c r="AO34" s="67"/>
+      <c r="AP34" s="67"/>
+      <c r="AQ34" s="67"/>
+      <c r="AR34" s="33"/>
+      <c r="AS34" s="33"/>
+      <c r="AT34" s="33"/>
+      <c r="AU34" s="33"/>
+      <c r="AV34" s="33"/>
+    </row>
+    <row r="35" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="32">
+        <v>46170</v>
+      </c>
+      <c r="G35" s="32">
+        <v>46173</v>
+      </c>
+      <c r="H35" s="31">
+        <v>4</v>
+      </c>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33"/>
+      <c r="AC35" s="33"/>
+      <c r="AD35" s="33"/>
+      <c r="AE35" s="33"/>
+      <c r="AF35" s="33"/>
+      <c r="AG35" s="33"/>
+      <c r="AH35" s="33"/>
+      <c r="AI35" s="33"/>
+      <c r="AJ35" s="33"/>
+      <c r="AK35" s="33"/>
+      <c r="AL35" s="33"/>
+      <c r="AM35" s="33"/>
+      <c r="AN35" s="33"/>
+      <c r="AO35" s="33"/>
+      <c r="AP35" s="33"/>
+      <c r="AQ35" s="68"/>
+      <c r="AR35" s="68"/>
+      <c r="AS35" s="68"/>
+      <c r="AT35" s="68"/>
+      <c r="AU35" s="33"/>
+      <c r="AV35" s="33"/>
+    </row>
+    <row r="36" spans="1:48" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="32">
+        <v>46175</v>
+      </c>
+      <c r="G36" s="32">
+        <v>46175</v>
+      </c>
+      <c r="H36" s="31">
         <v>1</v>
       </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
-      <c r="Z11" s="26"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-    </row>
-    <row r="12" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="20">
-        <v>46103</v>
-      </c>
-      <c r="G12" s="20">
-        <v>46107</v>
-      </c>
-      <c r="H12" s="21">
-        <v>5</v>
-      </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
-    </row>
-    <row r="13" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="29">
-        <v>46107</v>
-      </c>
-      <c r="G13" s="20">
-        <v>46107</v>
-      </c>
-      <c r="H13" s="21">
-        <v>1</v>
-      </c>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="26"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="26"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="26"/>
-      <c r="AB13" s="26"/>
-    </row>
-    <row r="14" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="26"/>
-      <c r="Y14" s="26"/>
-      <c r="Z14" s="26"/>
-      <c r="AA14" s="26"/>
-      <c r="AB14" s="26"/>
-    </row>
-    <row r="15" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="29">
-        <v>46107</v>
-      </c>
-      <c r="G15" s="20">
-        <v>46108</v>
-      </c>
-      <c r="H15" s="32">
-        <v>2</v>
-      </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="37"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="34"/>
-      <c r="AA15" s="26"/>
-      <c r="AB15" s="26"/>
-    </row>
-    <row r="16" spans="1:28" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="29">
-        <v>46108</v>
-      </c>
-      <c r="G16" s="20">
-        <v>46111</v>
-      </c>
-      <c r="H16" s="32">
-        <v>4</v>
-      </c>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="36"/>
-      <c r="AB16" s="26"/>
-    </row>
-    <row r="17" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="33">
-        <v>46108</v>
-      </c>
-      <c r="G17" s="33">
-        <v>46111</v>
-      </c>
-      <c r="H17" s="32">
-        <v>4</v>
-      </c>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="26"/>
-    </row>
-    <row r="18" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="33">
-        <v>46108</v>
-      </c>
-      <c r="G18" s="33">
-        <v>46111</v>
-      </c>
-      <c r="H18" s="32">
-        <v>4</v>
-      </c>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="26"/>
-    </row>
-    <row r="19" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="29">
-        <v>46111</v>
-      </c>
-      <c r="G19" s="20">
-        <v>46112</v>
-      </c>
-      <c r="H19" s="32">
-        <v>2</v>
-      </c>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
-      <c r="AA19" s="36"/>
-      <c r="AB19" s="36"/>
-    </row>
-    <row r="20" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="26"/>
-      <c r="W20" s="26"/>
-      <c r="X20" s="26"/>
-      <c r="Y20" s="26"/>
-      <c r="Z20" s="26"/>
-      <c r="AA20" s="26"/>
-      <c r="AB20" s="26"/>
-    </row>
-    <row r="21" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="33">
-        <v>46112</v>
-      </c>
-      <c r="G21" s="33">
-        <v>46112</v>
-      </c>
-      <c r="H21" s="32">
-        <v>1</v>
-      </c>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="36"/>
-    </row>
-    <row r="22" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="33">
-        <v>46112</v>
-      </c>
-      <c r="G22" s="33">
-        <v>46112</v>
-      </c>
-      <c r="H22" s="32">
-        <v>1</v>
-      </c>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="26"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="26"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="37"/>
-    </row>
-    <row r="23" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="33">
-        <v>46112</v>
-      </c>
-      <c r="G23" s="33">
-        <v>46112</v>
-      </c>
-      <c r="H23" s="32">
-        <v>1</v>
-      </c>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="26"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="26"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="36"/>
-    </row>
-    <row r="24" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="26"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="26"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-    </row>
-    <row r="25" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="W25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="34"/>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="34"/>
-    </row>
-    <row r="26" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="W26" s="34"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="34"/>
-      <c r="AA26" s="34"/>
-      <c r="AB26" s="34"/>
-    </row>
-    <row r="27" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="34"/>
-      <c r="AA27" s="34"/>
-      <c r="AB27" s="34"/>
-    </row>
-    <row r="28" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="W28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="34"/>
-      <c r="AA28" s="34"/>
-      <c r="AB28" s="34"/>
-    </row>
-    <row r="29" spans="1:28" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="W29" s="34"/>
-      <c r="X29" s="34"/>
-      <c r="Y29" s="34"/>
-      <c r="Z29" s="34"/>
-      <c r="AA29" s="34"/>
-      <c r="AB29" s="34"/>
-    </row>
-    <row r="30" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="34"/>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="34"/>
-      <c r="AA30" s="34"/>
-      <c r="AB30" s="34"/>
-    </row>
-    <row r="31" spans="1:28" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
-    </row>
-    <row r="32" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Y32" s="34"/>
-      <c r="Z32" s="34"/>
-      <c r="AA32" s="34"/>
-      <c r="AB32" s="34"/>
-    </row>
-    <row r="33" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="34"/>
-      <c r="Z33" s="34"/>
-      <c r="AA33" s="34"/>
-      <c r="AB33" s="34"/>
-    </row>
-    <row r="34" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="26"/>
-      <c r="W34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
-    </row>
-    <row r="35" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="26"/>
-      <c r="W35" s="34"/>
-      <c r="X35" s="34"/>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="34"/>
-      <c r="AA35" s="34"/>
-      <c r="AB35" s="34"/>
-    </row>
-    <row r="36" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="26"/>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
-    </row>
-    <row r="37" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="33"/>
+      <c r="Y36" s="33"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="33"/>
+      <c r="AC36" s="33"/>
+      <c r="AD36" s="33"/>
+      <c r="AE36" s="33"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="33"/>
+      <c r="AH36" s="33"/>
+      <c r="AI36" s="33"/>
+      <c r="AJ36" s="33"/>
+      <c r="AK36" s="33"/>
+      <c r="AL36" s="33"/>
+      <c r="AM36" s="33"/>
+      <c r="AN36" s="33"/>
+      <c r="AO36" s="33"/>
+      <c r="AP36" s="33"/>
+      <c r="AQ36" s="33"/>
+      <c r="AR36" s="33"/>
+      <c r="AS36" s="33"/>
+      <c r="AT36" s="33"/>
+      <c r="AU36" s="33"/>
+      <c r="AV36" s="68"/>
+    </row>
+    <row r="37" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD37" s="61"/>
+      <c r="AE37" s="61"/>
+      <c r="AF37" s="61"/>
+      <c r="AG37" s="61"/>
+      <c r="AH37" s="61"/>
+      <c r="AI37" s="61"/>
+      <c r="AJ37" s="61"/>
+      <c r="AK37" s="61"/>
+      <c r="AL37" s="61"/>
+      <c r="AM37" s="61"/>
+      <c r="AN37" s="61"/>
+      <c r="AO37" s="61"/>
+      <c r="AP37" s="61"/>
+      <c r="AQ37" s="61"/>
+      <c r="AR37" s="61"/>
+      <c r="AS37" s="61"/>
+      <c r="AT37" s="61"/>
+      <c r="AU37" s="61"/>
+      <c r="AV37" s="61"/>
+    </row>
+    <row r="38" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD38" s="61"/>
+      <c r="AE38" s="61"/>
+      <c r="AF38" s="61"/>
+      <c r="AG38" s="61"/>
+      <c r="AH38" s="61"/>
+      <c r="AI38" s="61"/>
+      <c r="AJ38" s="61"/>
+      <c r="AK38" s="61"/>
+      <c r="AL38" s="61"/>
+      <c r="AM38" s="61"/>
+      <c r="AN38" s="61"/>
+      <c r="AO38" s="61"/>
+      <c r="AP38" s="61"/>
+      <c r="AQ38" s="61"/>
+      <c r="AR38" s="61"/>
+      <c r="AS38" s="61"/>
+      <c r="AT38" s="61"/>
+      <c r="AU38" s="61"/>
+      <c r="AV38" s="61"/>
+    </row>
+    <row r="39" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD39" s="61"/>
+      <c r="AE39" s="61"/>
+      <c r="AF39" s="61"/>
+      <c r="AG39" s="61"/>
+      <c r="AH39" s="61"/>
+      <c r="AI39" s="61"/>
+      <c r="AJ39" s="61"/>
+      <c r="AK39" s="61"/>
+      <c r="AL39" s="61"/>
+      <c r="AM39" s="61"/>
+      <c r="AN39" s="61"/>
+      <c r="AO39" s="61"/>
+      <c r="AP39" s="61"/>
+      <c r="AQ39" s="61"/>
+      <c r="AR39" s="61"/>
+      <c r="AS39" s="61"/>
+      <c r="AT39" s="61"/>
+      <c r="AU39" s="61"/>
+      <c r="AV39" s="61"/>
+    </row>
+    <row r="40" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD40" s="61"/>
+      <c r="AE40" s="61"/>
+      <c r="AF40" s="61"/>
+      <c r="AG40" s="61"/>
+      <c r="AH40" s="61"/>
+      <c r="AI40" s="61"/>
+      <c r="AJ40" s="61"/>
+      <c r="AK40" s="61"/>
+      <c r="AL40" s="61"/>
+      <c r="AM40" s="61"/>
+      <c r="AN40" s="61"/>
+      <c r="AO40" s="61"/>
+      <c r="AP40" s="61"/>
+      <c r="AQ40" s="61"/>
+      <c r="AR40" s="61"/>
+      <c r="AS40" s="61"/>
+      <c r="AT40" s="61"/>
+      <c r="AU40" s="61"/>
+      <c r="AV40" s="61"/>
+    </row>
+    <row r="41" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD41" s="61"/>
+      <c r="AE41" s="61"/>
+      <c r="AF41" s="61"/>
+      <c r="AG41" s="61"/>
+      <c r="AH41" s="61"/>
+      <c r="AI41" s="61"/>
+      <c r="AJ41" s="61"/>
+      <c r="AK41" s="61"/>
+      <c r="AL41" s="61"/>
+      <c r="AM41" s="61"/>
+      <c r="AN41" s="61"/>
+      <c r="AO41" s="61"/>
+      <c r="AP41" s="61"/>
+      <c r="AQ41" s="61"/>
+      <c r="AR41" s="61"/>
+      <c r="AS41" s="61"/>
+      <c r="AT41" s="61"/>
+      <c r="AU41" s="61"/>
+      <c r="AV41" s="61"/>
+    </row>
+    <row r="42" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD42" s="61"/>
+      <c r="AE42" s="61"/>
+      <c r="AF42" s="61"/>
+      <c r="AG42" s="61"/>
+      <c r="AH42" s="61"/>
+      <c r="AI42" s="61"/>
+      <c r="AJ42" s="61"/>
+      <c r="AK42" s="61"/>
+      <c r="AL42" s="61"/>
+      <c r="AM42" s="61"/>
+      <c r="AN42" s="61"/>
+      <c r="AO42" s="61"/>
+      <c r="AP42" s="61"/>
+      <c r="AQ42" s="61"/>
+      <c r="AR42" s="61"/>
+      <c r="AS42" s="61"/>
+      <c r="AT42" s="61"/>
+      <c r="AU42" s="61"/>
+      <c r="AV42" s="61"/>
+    </row>
+    <row r="43" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD43" s="61"/>
+      <c r="AE43" s="61"/>
+      <c r="AF43" s="61"/>
+      <c r="AG43" s="61"/>
+      <c r="AH43" s="61"/>
+      <c r="AI43" s="61"/>
+      <c r="AJ43" s="61"/>
+      <c r="AK43" s="61"/>
+      <c r="AL43" s="61"/>
+      <c r="AM43" s="61"/>
+      <c r="AN43" s="61"/>
+      <c r="AO43" s="61"/>
+      <c r="AP43" s="61"/>
+      <c r="AQ43" s="61"/>
+      <c r="AR43" s="61"/>
+      <c r="AS43" s="61"/>
+      <c r="AT43" s="61"/>
+      <c r="AU43" s="61"/>
+      <c r="AV43" s="61"/>
+    </row>
+    <row r="44" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD44" s="61"/>
+      <c r="AE44" s="61"/>
+      <c r="AF44" s="61"/>
+      <c r="AG44" s="61"/>
+      <c r="AH44" s="61"/>
+      <c r="AI44" s="61"/>
+      <c r="AJ44" s="61"/>
+      <c r="AK44" s="61"/>
+      <c r="AL44" s="61"/>
+      <c r="AM44" s="61"/>
+      <c r="AN44" s="61"/>
+      <c r="AO44" s="61"/>
+      <c r="AP44" s="61"/>
+      <c r="AQ44" s="61"/>
+      <c r="AR44" s="61"/>
+      <c r="AS44" s="61"/>
+      <c r="AT44" s="61"/>
+      <c r="AU44" s="61"/>
+      <c r="AV44" s="61"/>
+    </row>
+    <row r="45" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD45" s="61"/>
+      <c r="AE45" s="61"/>
+      <c r="AF45" s="61"/>
+      <c r="AG45" s="61"/>
+      <c r="AH45" s="61"/>
+      <c r="AI45" s="61"/>
+      <c r="AJ45" s="61"/>
+      <c r="AK45" s="61"/>
+      <c r="AL45" s="61"/>
+      <c r="AM45" s="61"/>
+      <c r="AN45" s="61"/>
+      <c r="AO45" s="61"/>
+      <c r="AP45" s="61"/>
+      <c r="AQ45" s="61"/>
+      <c r="AR45" s="61"/>
+      <c r="AS45" s="61"/>
+      <c r="AT45" s="61"/>
+      <c r="AU45" s="61"/>
+      <c r="AV45" s="61"/>
+    </row>
+    <row r="46" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD46" s="61"/>
+      <c r="AE46" s="61"/>
+      <c r="AF46" s="61"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="61"/>
+      <c r="AK46" s="61"/>
+      <c r="AL46" s="61"/>
+      <c r="AM46" s="61"/>
+      <c r="AN46" s="61"/>
+      <c r="AO46" s="61"/>
+      <c r="AP46" s="61"/>
+      <c r="AQ46" s="61"/>
+      <c r="AR46" s="61"/>
+      <c r="AS46" s="61"/>
+      <c r="AT46" s="61"/>
+      <c r="AU46" s="61"/>
+      <c r="AV46" s="61"/>
+    </row>
+    <row r="47" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD47" s="61"/>
+      <c r="AE47" s="61"/>
+      <c r="AF47" s="61"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="61"/>
+      <c r="AL47" s="61"/>
+      <c r="AM47" s="61"/>
+      <c r="AN47" s="61"/>
+      <c r="AO47" s="61"/>
+      <c r="AP47" s="61"/>
+      <c r="AQ47" s="61"/>
+      <c r="AR47" s="61"/>
+      <c r="AS47" s="61"/>
+      <c r="AT47" s="61"/>
+      <c r="AU47" s="61"/>
+      <c r="AV47" s="61"/>
+    </row>
+    <row r="48" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD48" s="61"/>
+      <c r="AE48" s="61"/>
+      <c r="AF48" s="61"/>
+      <c r="AG48" s="61"/>
+      <c r="AH48" s="61"/>
+      <c r="AI48" s="61"/>
+      <c r="AJ48" s="61"/>
+      <c r="AK48" s="61"/>
+      <c r="AL48" s="61"/>
+      <c r="AM48" s="61"/>
+      <c r="AN48" s="61"/>
+      <c r="AO48" s="61"/>
+      <c r="AP48" s="61"/>
+      <c r="AQ48" s="61"/>
+      <c r="AR48" s="61"/>
+      <c r="AS48" s="61"/>
+      <c r="AT48" s="61"/>
+      <c r="AU48" s="61"/>
+      <c r="AV48" s="61"/>
+    </row>
+    <row r="49" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD49" s="61"/>
+      <c r="AE49" s="61"/>
+      <c r="AF49" s="61"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
+      <c r="AJ49" s="61"/>
+      <c r="AK49" s="61"/>
+      <c r="AL49" s="61"/>
+      <c r="AM49" s="61"/>
+      <c r="AN49" s="61"/>
+      <c r="AO49" s="61"/>
+      <c r="AP49" s="61"/>
+      <c r="AQ49" s="61"/>
+      <c r="AR49" s="61"/>
+      <c r="AS49" s="61"/>
+      <c r="AT49" s="61"/>
+      <c r="AU49" s="61"/>
+      <c r="AV49" s="61"/>
+    </row>
+    <row r="50" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD50" s="61"/>
+      <c r="AE50" s="61"/>
+      <c r="AF50" s="61"/>
+      <c r="AG50" s="61"/>
+      <c r="AH50" s="61"/>
+      <c r="AI50" s="61"/>
+      <c r="AJ50" s="61"/>
+      <c r="AK50" s="61"/>
+      <c r="AL50" s="61"/>
+      <c r="AM50" s="61"/>
+      <c r="AN50" s="61"/>
+      <c r="AO50" s="61"/>
+      <c r="AP50" s="61"/>
+      <c r="AQ50" s="61"/>
+      <c r="AR50" s="61"/>
+      <c r="AS50" s="61"/>
+      <c r="AT50" s="61"/>
+      <c r="AU50" s="61"/>
+      <c r="AV50" s="61"/>
+    </row>
+    <row r="51" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD51" s="61"/>
+      <c r="AE51" s="61"/>
+      <c r="AF51" s="61"/>
+      <c r="AG51" s="61"/>
+      <c r="AH51" s="61"/>
+      <c r="AI51" s="61"/>
+      <c r="AJ51" s="61"/>
+      <c r="AK51" s="61"/>
+      <c r="AL51" s="61"/>
+      <c r="AM51" s="61"/>
+      <c r="AN51" s="61"/>
+      <c r="AO51" s="61"/>
+      <c r="AP51" s="61"/>
+      <c r="AQ51" s="61"/>
+      <c r="AR51" s="61"/>
+      <c r="AS51" s="61"/>
+      <c r="AT51" s="61"/>
+      <c r="AU51" s="61"/>
+      <c r="AV51" s="61"/>
+    </row>
+    <row r="52" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
     </row>
-    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
     </row>
-    <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
     </row>
-    <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
     </row>
-    <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
     </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:48" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -7526,135 +10166,808 @@
       <c r="G989" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I3:AB3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:T2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="AC1:AC6"/>
+    <mergeCell ref="AD3:AT3"/>
   </mergeCells>
   <conditionalFormatting sqref="I3">
-    <cfRule type="expression" dxfId="24" priority="29">
+    <cfRule type="expression" dxfId="167" priority="171">
       <formula>I$4&lt;=EOMONTH($I$4,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="expression" dxfId="23" priority="30">
+    <cfRule type="expression" dxfId="166" priority="172">
       <formula>AND(I$4&lt;=EOMONTH($I$4,1),I$4&gt;EOMONTH($I$4,0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:AA23">
-    <cfRule type="expression" dxfId="22" priority="31">
+  <conditionalFormatting sqref="I4:AA5 I7:AA23">
+    <cfRule type="expression" dxfId="165" priority="173">
       <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:AB23 I25:AB25">
-    <cfRule type="expression" dxfId="21" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="175" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo bajo",I$4&gt;=$F7,I$4&lt;=$F7+$H7-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:AB23 I25:AB25">
-    <cfRule type="expression" dxfId="20" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="176" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo alto",I$4&gt;=$F7,I$4&lt;=$F7+$H7-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:AB23 I25:AB25">
-    <cfRule type="expression" dxfId="19" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="177" stopIfTrue="1">
       <formula>AND(#REF!="Según lo previsto",I$4&gt;=$F7,I$4&lt;=$F7+$H7-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:AB23 I25:AB25">
-    <cfRule type="expression" dxfId="18" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="178" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo medio",I$4&gt;=$F7,I$4&lt;=$F7+$H7-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:AB23 I25:AB25">
-    <cfRule type="expression" dxfId="17" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="179" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$4&gt;=$F7,I$4&lt;=$F7+$H7-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB4:AB23">
-    <cfRule type="expression" dxfId="16" priority="41">
+  <conditionalFormatting sqref="AB4:AB5 AB7:AB23">
+    <cfRule type="expression" dxfId="159" priority="183">
       <formula>AND(TODAY()&gt;=AB$4,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:AA25">
-    <cfRule type="expression" dxfId="15" priority="22">
+    <cfRule type="expression" dxfId="158" priority="164">
       <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB25">
-    <cfRule type="expression" dxfId="14" priority="28">
+    <cfRule type="expression" dxfId="157" priority="170">
       <formula>AND(TODAY()&gt;=AB$4,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:AA24">
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="156" priority="150">
       <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:AB24">
-    <cfRule type="expression" dxfId="12" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="151" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo bajo",I$4&gt;=$F24,I$4&lt;=$F24+$H24-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:AB24">
-    <cfRule type="expression" dxfId="11" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="152" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo alto",I$4&gt;=$F24,I$4&lt;=$F24+$H24-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:AB24">
-    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="153" stopIfTrue="1">
       <formula>AND(#REF!="Según lo previsto",I$4&gt;=$F24,I$4&lt;=$F24+$H24-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:AB24">
-    <cfRule type="expression" dxfId="9" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="154" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo medio",I$4&gt;=$F24,I$4&lt;=$F24+$H24-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:AB24">
-    <cfRule type="expression" dxfId="8" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="155" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$4&gt;=$F24,I$4&lt;=$F24+$H24-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB24">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="150" priority="156">
       <formula>AND(TODAY()&gt;=AB$4,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:AA36">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="149" priority="143">
       <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:AB36">
-    <cfRule type="expression" dxfId="5" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="144" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo bajo",I$4&gt;=$F26,I$4&lt;=$F26+$H26-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:AB36">
-    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="145" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo alto",I$4&gt;=$F26,I$4&lt;=$F26+$H26-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:AB36">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="146" stopIfTrue="1">
       <formula>AND(#REF!="Según lo previsto",I$4&gt;=$F26,I$4&lt;=$F26+$H26-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:AB36">
-    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="147" stopIfTrue="1">
       <formula>AND(#REF!="Riesgo medio",I$4&gt;=$F26,I$4&lt;=$F26+$H26-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:AB36">
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="148" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$4&gt;=$F26,I$4&lt;=$F26+$H26-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB26:AB36">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="143" priority="149">
       <formula>AND(TODAY()&gt;=AB$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE4:AS5 AE7:AS23">
+    <cfRule type="expression" dxfId="142" priority="136">
+      <formula>AND(TODAY()&gt;=AE$4,TODAY()&lt;AF$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AT23 AE25:AT25">
+    <cfRule type="expression" dxfId="141" priority="137" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AE$4&gt;=$F7,AE$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AT23 AE25:AT25">
+    <cfRule type="expression" dxfId="140" priority="138" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AE$4&gt;=$F7,AE$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AT23 AE25:AT25">
+    <cfRule type="expression" dxfId="139" priority="139" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AE$4&gt;=$F7,AE$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AT23 AE25:AT25">
+    <cfRule type="expression" dxfId="138" priority="140" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AE$4&gt;=$F7,AE$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AT23 AE25:AT25">
+    <cfRule type="expression" dxfId="137" priority="141" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AE$4&gt;=$F7,AE$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT4:AT5 AT7:AT23">
+    <cfRule type="expression" dxfId="136" priority="142">
+      <formula>AND(TODAY()&gt;=AT$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE25:AS25">
+    <cfRule type="expression" dxfId="135" priority="134">
+      <formula>AND(TODAY()&gt;=AE$4,TODAY()&lt;AF$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT25">
+    <cfRule type="expression" dxfId="134" priority="135">
+      <formula>AND(TODAY()&gt;=AT$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AS24">
+    <cfRule type="expression" dxfId="133" priority="127">
+      <formula>AND(TODAY()&gt;=AE$4,TODAY()&lt;AF$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AT24">
+    <cfRule type="expression" dxfId="132" priority="128" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AE$4&gt;=$F24,AE$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AT24">
+    <cfRule type="expression" dxfId="131" priority="129" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AE$4&gt;=$F24,AE$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AT24">
+    <cfRule type="expression" dxfId="130" priority="130" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AE$4&gt;=$F24,AE$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AT24">
+    <cfRule type="expression" dxfId="129" priority="131" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AE$4&gt;=$F24,AE$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AT24">
+    <cfRule type="expression" dxfId="128" priority="132" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AE$4&gt;=$F24,AE$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT24">
+    <cfRule type="expression" dxfId="127" priority="133">
+      <formula>AND(TODAY()&gt;=AT$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AS28 AE30:AS36 AE29:AF29 AH29:AS29">
+    <cfRule type="expression" dxfId="126" priority="120">
+      <formula>AND(TODAY()&gt;=AE$4,TODAY()&lt;AF$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AT28 AE30:AT36 AE29:AF29 AH29:AT29">
+    <cfRule type="expression" dxfId="125" priority="121" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AE$4&gt;=$F26,AE$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AT28 AE30:AT36 AE29:AF29 AH29:AT29">
+    <cfRule type="expression" dxfId="124" priority="122" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AE$4&gt;=$F26,AE$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AT28 AE30:AT36 AE29:AF29 AH29:AT29">
+    <cfRule type="expression" dxfId="123" priority="123" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AE$4&gt;=$F26,AE$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AT28 AE30:AT36 AE29:AF29 AH29:AT29">
+    <cfRule type="expression" dxfId="122" priority="124" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AE$4&gt;=$F26,AE$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AT28 AE30:AT36 AE29:AF29 AH29:AT29">
+    <cfRule type="expression" dxfId="121" priority="125" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AE$4&gt;=$F26,AE$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT26:AT36">
+    <cfRule type="expression" dxfId="120" priority="126">
+      <formula>AND(TODAY()&gt;=AT$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC23 AC25">
+    <cfRule type="expression" dxfId="119" priority="114" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AC$4&gt;=$F7,AC$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC23 AC25">
+    <cfRule type="expression" dxfId="118" priority="115" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AC$4&gt;=$F7,AC$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC23 AC25">
+    <cfRule type="expression" dxfId="117" priority="116" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AC$4&gt;=$F7,AC$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC23 AC25">
+    <cfRule type="expression" dxfId="116" priority="117" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AC$4&gt;=$F7,AC$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC23 AC25">
+    <cfRule type="expression" dxfId="115" priority="118" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AC$4&gt;=$F7,AC$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC23">
+    <cfRule type="expression" dxfId="114" priority="119">
+      <formula>AND(TODAY()&gt;=AC$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC25">
+    <cfRule type="expression" dxfId="113" priority="113">
+      <formula>AND(TODAY()&gt;=AC$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24">
+    <cfRule type="expression" dxfId="112" priority="107" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AC$4&gt;=$F24,AC$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24">
+    <cfRule type="expression" dxfId="111" priority="108" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AC$4&gt;=$F24,AC$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24">
+    <cfRule type="expression" dxfId="110" priority="109" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AC$4&gt;=$F24,AC$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24">
+    <cfRule type="expression" dxfId="109" priority="110" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AC$4&gt;=$F24,AC$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24">
+    <cfRule type="expression" dxfId="108" priority="111" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AC$4&gt;=$F24,AC$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC24">
+    <cfRule type="expression" dxfId="107" priority="112">
+      <formula>AND(TODAY()&gt;=AC$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC26:AC36">
+    <cfRule type="expression" dxfId="106" priority="101" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AC$4&gt;=$F26,AC$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC26:AC36">
+    <cfRule type="expression" dxfId="105" priority="102" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AC$4&gt;=$F26,AC$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC26:AC36">
+    <cfRule type="expression" dxfId="104" priority="103" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AC$4&gt;=$F26,AC$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC26:AC36">
+    <cfRule type="expression" dxfId="103" priority="104" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AC$4&gt;=$F26,AC$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC26:AC36">
+    <cfRule type="expression" dxfId="102" priority="105" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AC$4&gt;=$F26,AC$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC26:AC36">
+    <cfRule type="expression" dxfId="101" priority="106">
+      <formula>AND(TODAY()&gt;=AC$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="100" priority="38">
+      <formula>AND(TODAY()&gt;=AD$4,TODAY()&lt;AE$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 P6 W6">
+    <cfRule type="expression" dxfId="97" priority="93" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",I$4&gt;=$F6,I$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 P6 W6">
+    <cfRule type="expression" dxfId="96" priority="94" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",I$4&gt;=$F6,I$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 P6 W6">
+    <cfRule type="expression" dxfId="95" priority="95" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",I$4&gt;=$F6,I$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 P6 W6">
+    <cfRule type="expression" dxfId="94" priority="96" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",I$4&gt;=$F6,I$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 P6 W6">
+    <cfRule type="expression" dxfId="93" priority="97" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,I$4&gt;=$F6,I$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 P6 W6">
+    <cfRule type="expression" dxfId="92" priority="98">
+      <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:O6 R6:V6 Y6:AB6">
+    <cfRule type="expression" dxfId="91" priority="87">
+      <formula>AND(TODAY()&gt;=K$4,TODAY()&lt;L$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:O6 R6:V6 Y6:AB6">
+    <cfRule type="expression" dxfId="90" priority="88" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",K$4&gt;=$F6,K$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:O6 R6:V6 Y6:AB6">
+    <cfRule type="expression" dxfId="89" priority="89" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",K$4&gt;=$F6,K$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:O6 R6:V6 Y6:AB6">
+    <cfRule type="expression" dxfId="88" priority="90" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",K$4&gt;=$F6,K$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:O6 R6:V6 Y6:AB6">
+    <cfRule type="expression" dxfId="87" priority="91" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",K$4&gt;=$F6,K$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:O6 R6:V6 Y6:AB6">
+    <cfRule type="expression" dxfId="86" priority="92" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,K$4&gt;=$F6,K$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 Q6 X6">
+    <cfRule type="expression" dxfId="85" priority="81" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",J$4&gt;=$F6,J$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 Q6 X6">
+    <cfRule type="expression" dxfId="84" priority="82" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",J$4&gt;=$F6,J$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 Q6 X6">
+    <cfRule type="expression" dxfId="83" priority="83" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",J$4&gt;=$F6,J$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 Q6 X6">
+    <cfRule type="expression" dxfId="82" priority="84" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",J$4&gt;=$F6,J$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 Q6 X6">
+    <cfRule type="expression" dxfId="81" priority="85" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,J$4&gt;=$F6,J$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 Q6 X6">
+    <cfRule type="expression" dxfId="80" priority="86">
+      <formula>AND(TODAY()&gt;=J$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6 AQ6">
+    <cfRule type="expression" dxfId="79" priority="75" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AJ$4&gt;=$F6,AJ$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6 AQ6">
+    <cfRule type="expression" dxfId="78" priority="76" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AJ$4&gt;=$F6,AJ$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6 AQ6">
+    <cfRule type="expression" dxfId="77" priority="77" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AJ$4&gt;=$F6,AJ$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6 AQ6">
+    <cfRule type="expression" dxfId="76" priority="78" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AJ$4&gt;=$F6,AJ$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6 AQ6">
+    <cfRule type="expression" dxfId="75" priority="79" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AJ$4&gt;=$F6,AJ$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6 AQ6">
+    <cfRule type="expression" dxfId="74" priority="80">
+      <formula>AND(TODAY()&gt;=AJ$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AI6 AL6:AP6 AS6:AT6">
+    <cfRule type="expression" dxfId="73" priority="69">
+      <formula>AND(TODAY()&gt;=AE$4,TODAY()&lt;AF$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AI6 AL6:AP6 AS6:AT6">
+    <cfRule type="expression" dxfId="72" priority="70" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AE$4&gt;=$F6,AE$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AI6 AL6:AP6 AS6:AT6">
+    <cfRule type="expression" dxfId="71" priority="71" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AE$4&gt;=$F6,AE$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AI6 AL6:AP6 AS6:AT6">
+    <cfRule type="expression" dxfId="70" priority="72" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AE$4&gt;=$F6,AE$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AI6 AL6:AP6 AS6:AT6">
+    <cfRule type="expression" dxfId="69" priority="73" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AE$4&gt;=$F6,AE$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AI6 AL6:AP6 AS6:AT6">
+    <cfRule type="expression" dxfId="68" priority="74" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AE$4&gt;=$F6,AE$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6 AR6">
+    <cfRule type="expression" dxfId="67" priority="63" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AK$4&gt;=$F6,AK$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6 AR6">
+    <cfRule type="expression" dxfId="66" priority="64" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AK$4&gt;=$F6,AK$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6 AR6">
+    <cfRule type="expression" dxfId="65" priority="65" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AK$4&gt;=$F6,AK$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6 AR6">
+    <cfRule type="expression" dxfId="64" priority="66" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AK$4&gt;=$F6,AK$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6 AR6">
+    <cfRule type="expression" dxfId="63" priority="67" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AK$4&gt;=$F6,AK$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6 AR6">
+    <cfRule type="expression" dxfId="62" priority="68">
+      <formula>AND(TODAY()&gt;=AK$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD4:AD5 AD7:AD23">
+    <cfRule type="expression" dxfId="61" priority="57">
+      <formula>AND(TODAY()&gt;=AD$4,TODAY()&lt;AE$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD23 AD25">
+    <cfRule type="expression" dxfId="60" priority="58" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AD$4&gt;=$F7,AD$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD23 AD25">
+    <cfRule type="expression" dxfId="59" priority="59" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AD$4&gt;=$F7,AD$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD23 AD25">
+    <cfRule type="expression" dxfId="58" priority="60" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AD$4&gt;=$F7,AD$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD23 AD25">
+    <cfRule type="expression" dxfId="57" priority="61" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AD$4&gt;=$F7,AD$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD23 AD25">
+    <cfRule type="expression" dxfId="56" priority="62" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AD$4&gt;=$F7,AD$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD25">
+    <cfRule type="expression" dxfId="55" priority="56">
+      <formula>AND(TODAY()&gt;=AD$4,TODAY()&lt;AE$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24">
+    <cfRule type="expression" dxfId="54" priority="50">
+      <formula>AND(TODAY()&gt;=AD$4,TODAY()&lt;AE$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24">
+    <cfRule type="expression" dxfId="53" priority="51" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AD$4&gt;=$F24,AD$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24">
+    <cfRule type="expression" dxfId="52" priority="52" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AD$4&gt;=$F24,AD$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24">
+    <cfRule type="expression" dxfId="51" priority="53" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AD$4&gt;=$F24,AD$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24">
+    <cfRule type="expression" dxfId="50" priority="54" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AD$4&gt;=$F24,AD$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24">
+    <cfRule type="expression" dxfId="49" priority="55" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AD$4&gt;=$F24,AD$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD36">
+    <cfRule type="expression" dxfId="48" priority="44">
+      <formula>AND(TODAY()&gt;=AD$4,TODAY()&lt;AE$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD36">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AD$4&gt;=$F26,AD$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD36">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AD$4&gt;=$F26,AD$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD36">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AD$4&gt;=$F26,AD$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD36">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AD$4&gt;=$F26,AD$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD36">
+    <cfRule type="expression" dxfId="43" priority="49" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AD$4&gt;=$F26,AD$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="41" priority="39" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AD$4&gt;=$F6,AD$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="40" priority="40" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AD$4&gt;=$F6,AD$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="39" priority="41" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AD$4&gt;=$F6,AD$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="38" priority="42" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AD$4&gt;=$F6,AD$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="37" priority="43" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AD$4&gt;=$F6,AD$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU7:AV23 AU25:AV25">
+    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AU$4&gt;=$F7,AU$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU7:AV23 AU25:AV25">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AU$4&gt;=$F7,AU$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU7:AV23 AU25:AV25">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AU$4&gt;=$F7,AU$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU7:AV23 AU25:AV25">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AU$4&gt;=$F7,AU$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU7:AV23 AU25:AV25">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AU$4&gt;=$F7,AU$4&lt;=$F7+$H7-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU4:AV5 AU7:AV23">
+    <cfRule type="expression" dxfId="31" priority="37">
+      <formula>AND(TODAY()&gt;=AU$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU25:AV25">
+    <cfRule type="expression" dxfId="30" priority="31">
+      <formula>AND(TODAY()&gt;=AU$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU24:AV24">
+    <cfRule type="expression" dxfId="29" priority="25" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AU$4&gt;=$F24,AU$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU24:AV24">
+    <cfRule type="expression" dxfId="28" priority="26" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AU$4&gt;=$F24,AU$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU24:AV24">
+    <cfRule type="expression" dxfId="27" priority="27" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AU$4&gt;=$F24,AU$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU24:AV24">
+    <cfRule type="expression" dxfId="26" priority="28" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AU$4&gt;=$F24,AU$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU24:AV24">
+    <cfRule type="expression" dxfId="25" priority="29" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AU$4&gt;=$F24,AU$4&lt;=$F24+$H24-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU24:AV24">
+    <cfRule type="expression" dxfId="24" priority="30">
+      <formula>AND(TODAY()&gt;=AU$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU26:AV36">
+    <cfRule type="expression" dxfId="23" priority="19" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AU$4&gt;=$F26,AU$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU26:AV36">
+    <cfRule type="expression" dxfId="22" priority="20" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AU$4&gt;=$F26,AU$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU26:AV36">
+    <cfRule type="expression" dxfId="21" priority="21" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AU$4&gt;=$F26,AU$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU26:AV36">
+    <cfRule type="expression" dxfId="20" priority="22" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AU$4&gt;=$F26,AU$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU26:AV36">
+    <cfRule type="expression" dxfId="19" priority="23" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AU$4&gt;=$F26,AU$4&lt;=$F26+$H26-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU26:AV36">
+    <cfRule type="expression" dxfId="18" priority="24">
+      <formula>AND(TODAY()&gt;=AU$4,TODAY()&lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU6:AV6">
+    <cfRule type="expression" dxfId="17" priority="13">
+      <formula>AND(TODAY()&gt;=AU$4,TODAY()&lt;AV$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU6:AV6">
+    <cfRule type="expression" dxfId="16" priority="14" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AU$4&gt;=$F6,AU$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU6:AV6">
+    <cfRule type="expression" dxfId="15" priority="15" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AU$4&gt;=$F6,AU$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU6:AV6">
+    <cfRule type="expression" dxfId="14" priority="16" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AU$4&gt;=$F6,AU$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU6:AV6">
+    <cfRule type="expression" dxfId="13" priority="17" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AU$4&gt;=$F6,AU$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU6:AV6">
+    <cfRule type="expression" dxfId="12" priority="18" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AU$4&gt;=$F6,AU$4&lt;=$F6+$H6-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG29">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo bajo",AG$4&gt;=$F29,AG$4&lt;=$F29+$H29-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG29">
+    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo alto",AG$4&gt;=$F29,AG$4&lt;=$F29+$H29-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG29">
+    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
+      <formula>AND(#REF!="Según lo previsto",AG$4&gt;=$F29,AG$4&lt;=$F29+$H29-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG29">
+    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
+      <formula>AND(#REF!="Riesgo medio",AG$4&gt;=$F29,AG$4&lt;=$F29+$H29-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG29">
+    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,AG$4&gt;=$F29,AG$4&lt;=$F29+$H29-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG29">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>AND(TODAY()&gt;=AG$4,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -7679,198 +10992,198 @@
   <dimension ref="B2:M13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="45" customWidth="1"/>
-    <col min="2" max="2" width="57.21875" style="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" style="45" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" style="51" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" style="52" customWidth="1"/>
-    <col min="6" max="6" width="14" style="45" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="45" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="45"/>
+    <col min="1" max="1" width="2.88671875" style="43" customWidth="1"/>
+    <col min="2" max="2" width="57.21875" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="43" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="49" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" style="50" customWidth="1"/>
+    <col min="6" max="6" width="14" style="43" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="43" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="43"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" s="41" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="38" t="s">
+    <row r="2" spans="2:13" s="39" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="43">
+      <c r="D3" s="41">
         <v>2</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="42">
         <f t="shared" ref="E3:E12" si="0">D3*7291</f>
         <v>14582</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="42" t="s">
+      <c r="B4" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="43">
+      <c r="D4" s="41">
         <v>4</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="42">
         <f t="shared" si="0"/>
         <v>29164</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="42" t="s">
+      <c r="B5" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="41">
         <v>5</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="42">
         <f t="shared" si="0"/>
         <v>36455</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="42" t="s">
+      <c r="B6" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="41">
         <v>3</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="42">
         <f t="shared" si="0"/>
         <v>21873</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="42" t="s">
+      <c r="B7" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="41">
         <v>6</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="42">
         <f t="shared" si="0"/>
         <v>43746</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="41">
         <v>7</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="42">
         <f t="shared" si="0"/>
         <v>51037</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="42" t="s">
+      <c r="B9" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="41">
         <v>7</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="42">
         <f t="shared" si="0"/>
         <v>51037</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="43">
+      <c r="B10" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="41">
         <v>7</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="42">
         <f t="shared" si="0"/>
         <v>51037</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="42" t="s">
+      <c r="B11" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="41">
         <v>8</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="42">
         <f t="shared" si="0"/>
         <v>58328</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="43">
+      <c r="B12" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="41">
         <v>1</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="42">
         <f t="shared" si="0"/>
         <v>7291</v>
       </c>
     </row>
-    <row r="13" spans="2:13" s="50" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48">
+    <row r="13" spans="2:13" s="48" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46">
         <f>SUM(D3:D12)</f>
         <v>50</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="47">
         <f>E3+E4+E5+E6+E7+E8+E9+E10+E11</f>
         <v>357259</v>
       </c>
